--- a/storage/app/public/vocabs/geologicalage/1.4/geologicalage_1-4.xlsx
+++ b/storage/app/public/vocabs/geologicalage/1.4/geologicalage_1-4.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="541">
   <si>
     <t>synonyms</t>
   </si>
@@ -23,12 +23,12 @@
     <t>uri</t>
   </si>
   <si>
-    <t>hyperlink</t>
-  </si>
-  <si>
     <t>external_uri</t>
   </si>
   <si>
+    <t>external_vocab_scheme</t>
+  </si>
+  <si>
     <t>present-day</t>
   </si>
   <si>
@@ -39,6 +39,9 @@
   </si>
   <si>
     <t>http://resource.geosciml.org/classifier/ics/ischart/Present</t>
+  </si>
+  <si>
+    <t>geosciml</t>
   </si>
   <si>
     <t>Phanerozoic</t>
@@ -2019,1959 +2022,2487 @@
       <c r="H2" t="s">
         <v>6</v>
       </c>
+      <c r="I2" t="s">
+        <v>7</v>
+      </c>
       <c r="J2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>11</v>
       </c>
       <c r="J3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I4" t="s">
+        <v>15</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="D6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="D7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="E8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
       </c>
       <c r="J9" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="E10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
       </c>
       <c r="J10" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="E11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="I11" t="s">
+        <v>36</v>
       </c>
       <c r="J11" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="C12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="I12" t="s">
+        <v>39</v>
       </c>
       <c r="J12" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="D13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="I13" t="s">
+        <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="E14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
+        <v>45</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="E15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H15" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="I15" t="s">
+        <v>48</v>
       </c>
       <c r="J15" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="D16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="I16" t="s">
+        <v>51</v>
       </c>
       <c r="J16" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="E17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="I17" t="s">
+        <v>54</v>
       </c>
       <c r="J17" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="E18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H18" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="I18" t="s">
+        <v>57</v>
       </c>
       <c r="J18" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="E19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="I19" t="s">
+        <v>60</v>
       </c>
       <c r="J19" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="E20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H20" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="I20" t="s">
+        <v>63</v>
       </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="E21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H21" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="I21" t="s">
+        <v>66</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="E22" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H22" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="I22" t="s">
+        <v>69</v>
       </c>
       <c r="J22" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="C23" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H23" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="I23" t="s">
+        <v>72</v>
       </c>
       <c r="J23" t="s">
-        <v>71</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="D24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H24" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="I24" t="s">
+        <v>75</v>
       </c>
       <c r="J24" t="s">
-        <v>74</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="E25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="I25" t="s">
+        <v>78</v>
       </c>
       <c r="J25" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="E26" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="I26" t="s">
+        <v>81</v>
       </c>
       <c r="J26" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="D27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="I27" t="s">
+        <v>84</v>
       </c>
       <c r="J27" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="E28" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H28" t="s">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="I28" t="s">
+        <v>87</v>
       </c>
       <c r="J28" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="E29" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="I29" t="s">
+        <v>90</v>
       </c>
       <c r="J29" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="E30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H30" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="I30" t="s">
+        <v>93</v>
       </c>
       <c r="J30" t="s">
-        <v>92</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="E31" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="I31" t="s">
+        <v>96</v>
       </c>
       <c r="J31" t="s">
-        <v>95</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="D32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H32" t="s">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="I32" t="s">
+        <v>99</v>
       </c>
       <c r="J32" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="E33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H33" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+      <c r="I33" t="s">
+        <v>102</v>
       </c>
       <c r="J33" t="s">
-        <v>101</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="E34" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H34" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="I34" t="s">
+        <v>105</v>
       </c>
       <c r="J34" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="E35" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H35" t="s">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="I35" t="s">
+        <v>108</v>
       </c>
       <c r="J35" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="B36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H36" t="s">
-        <v>109</v>
+        <v>110</v>
+      </c>
+      <c r="I36" t="s">
+        <v>111</v>
       </c>
       <c r="J36" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="C37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H37" t="s">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="I37" t="s">
+        <v>114</v>
       </c>
       <c r="J37" t="s">
-        <v>113</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="D38" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="I38" t="s">
+        <v>117</v>
       </c>
       <c r="J38" t="s">
-        <v>116</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="E39" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" t="s">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="I39" t="s">
+        <v>120</v>
       </c>
       <c r="J39" t="s">
-        <v>119</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="E40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H40" t="s">
-        <v>121</v>
+        <v>122</v>
+      </c>
+      <c r="I40" t="s">
+        <v>123</v>
       </c>
       <c r="J40" t="s">
-        <v>122</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="E41" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H41" t="s">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="I41" t="s">
+        <v>126</v>
       </c>
       <c r="J41" t="s">
-        <v>125</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="E42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H42" t="s">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="I42" t="s">
+        <v>129</v>
       </c>
       <c r="J42" t="s">
-        <v>128</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="E43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H43" t="s">
-        <v>130</v>
+        <v>131</v>
+      </c>
+      <c r="I43" t="s">
+        <v>132</v>
       </c>
       <c r="J43" t="s">
-        <v>131</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="E44" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H44" t="s">
-        <v>133</v>
+        <v>134</v>
+      </c>
+      <c r="I44" t="s">
+        <v>135</v>
       </c>
       <c r="J44" t="s">
-        <v>134</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="D45" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H45" t="s">
-        <v>136</v>
+        <v>137</v>
+      </c>
+      <c r="I45" t="s">
+        <v>138</v>
       </c>
       <c r="J45" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="E46" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H46" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="I46" t="s">
+        <v>141</v>
       </c>
       <c r="J46" t="s">
-        <v>140</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="E47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H47" t="s">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="I47" t="s">
+        <v>144</v>
       </c>
       <c r="J47" t="s">
-        <v>143</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="E48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H48" t="s">
-        <v>145</v>
+        <v>146</v>
+      </c>
+      <c r="I48" t="s">
+        <v>147</v>
       </c>
       <c r="J48" t="s">
-        <v>146</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="E49" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H49" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="I49" t="s">
+        <v>150</v>
       </c>
       <c r="J49" t="s">
-        <v>149</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="E50" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H50" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="I50" t="s">
+        <v>153</v>
       </c>
       <c r="J50" t="s">
-        <v>152</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="E51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H51" t="s">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="I51" t="s">
+        <v>156</v>
       </c>
       <c r="J51" t="s">
-        <v>155</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="C52" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H52" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="I52" t="s">
+        <v>159</v>
       </c>
       <c r="J52" t="s">
-        <v>158</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="D53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H53" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="I53" t="s">
+        <v>162</v>
       </c>
       <c r="J53" t="s">
-        <v>161</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="E54" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H54" t="s">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="I54" t="s">
+        <v>165</v>
       </c>
       <c r="J54" t="s">
-        <v>164</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="E55" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H55" t="s">
-        <v>166</v>
+        <v>167</v>
+      </c>
+      <c r="I55" t="s">
+        <v>168</v>
       </c>
       <c r="J55" t="s">
-        <v>167</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="E56" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H56" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="I56" t="s">
+        <v>171</v>
       </c>
       <c r="J56" t="s">
-        <v>170</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="D57" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H57" t="s">
-        <v>172</v>
+        <v>173</v>
+      </c>
+      <c r="I57" t="s">
+        <v>174</v>
       </c>
       <c r="J57" t="s">
-        <v>173</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="E58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H58" t="s">
-        <v>175</v>
+        <v>176</v>
+      </c>
+      <c r="I58" t="s">
+        <v>177</v>
       </c>
       <c r="J58" t="s">
-        <v>176</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="E59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H59" t="s">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="I59" t="s">
+        <v>180</v>
       </c>
       <c r="J59" t="s">
-        <v>179</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="E60" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H60" t="s">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="I60" t="s">
+        <v>183</v>
       </c>
       <c r="J60" t="s">
-        <v>182</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="E61" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H61" t="s">
-        <v>184</v>
+        <v>185</v>
+      </c>
+      <c r="I61" t="s">
+        <v>186</v>
       </c>
       <c r="J61" t="s">
-        <v>185</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="D62" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H62" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="I62" t="s">
+        <v>189</v>
       </c>
       <c r="J62" t="s">
-        <v>188</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="E63" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H63" t="s">
-        <v>190</v>
+        <v>191</v>
+      </c>
+      <c r="I63" t="s">
+        <v>192</v>
       </c>
       <c r="J63" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="E64" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H64" t="s">
-        <v>193</v>
+        <v>194</v>
+      </c>
+      <c r="I64" t="s">
+        <v>195</v>
       </c>
       <c r="J64" t="s">
-        <v>194</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="E65" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H65" t="s">
-        <v>196</v>
+        <v>197</v>
+      </c>
+      <c r="I65" t="s">
+        <v>198</v>
       </c>
       <c r="J65" t="s">
-        <v>197</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="E66" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H66" t="s">
-        <v>199</v>
+        <v>200</v>
+      </c>
+      <c r="I66" t="s">
+        <v>201</v>
       </c>
       <c r="J66" t="s">
-        <v>200</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="C67" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H67" t="s">
-        <v>202</v>
+        <v>203</v>
+      </c>
+      <c r="I67" t="s">
+        <v>204</v>
       </c>
       <c r="J67" t="s">
-        <v>203</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="D68" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H68" t="s">
-        <v>205</v>
+        <v>206</v>
+      </c>
+      <c r="I68" t="s">
+        <v>207</v>
       </c>
       <c r="J68" t="s">
-        <v>206</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="E69" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H69" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="I69" t="s">
+        <v>210</v>
       </c>
       <c r="J69" t="s">
-        <v>209</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="E70" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H70" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="I70" t="s">
+        <v>213</v>
       </c>
       <c r="J70" t="s">
-        <v>212</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="E71" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H71" t="s">
-        <v>214</v>
+        <v>215</v>
+      </c>
+      <c r="I71" t="s">
+        <v>216</v>
       </c>
       <c r="J71" t="s">
-        <v>215</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="D72" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H72" t="s">
-        <v>217</v>
+        <v>218</v>
+      </c>
+      <c r="I72" t="s">
+        <v>219</v>
       </c>
       <c r="J72" t="s">
-        <v>218</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="E73" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H73" t="s">
-        <v>220</v>
+        <v>221</v>
+      </c>
+      <c r="I73" t="s">
+        <v>222</v>
       </c>
       <c r="J73" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="E74" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H74" t="s">
-        <v>223</v>
+        <v>224</v>
+      </c>
+      <c r="I74" t="s">
+        <v>225</v>
       </c>
       <c r="J74" t="s">
-        <v>224</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="D75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H75" t="s">
-        <v>226</v>
+        <v>227</v>
+      </c>
+      <c r="I75" t="s">
+        <v>228</v>
       </c>
       <c r="J75" t="s">
-        <v>227</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="E76" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H76" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="I76" t="s">
+        <v>231</v>
       </c>
       <c r="J76" t="s">
-        <v>230</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="E77" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H77" t="s">
-        <v>232</v>
+        <v>233</v>
+      </c>
+      <c r="I77" t="s">
+        <v>234</v>
       </c>
       <c r="J77" t="s">
-        <v>233</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="B78" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H78" t="s">
-        <v>235</v>
+        <v>236</v>
+      </c>
+      <c r="I78" t="s">
+        <v>237</v>
       </c>
       <c r="J78" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="C79" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H79" t="s">
-        <v>239</v>
+        <v>240</v>
+      </c>
+      <c r="I79" t="s">
+        <v>241</v>
       </c>
       <c r="J79" t="s">
-        <v>240</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="D80" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H80" t="s">
-        <v>242</v>
+        <v>243</v>
+      </c>
+      <c r="I80" t="s">
+        <v>244</v>
       </c>
       <c r="J80" t="s">
-        <v>243</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="E81" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H81" t="s">
-        <v>245</v>
+        <v>246</v>
+      </c>
+      <c r="I81" t="s">
+        <v>247</v>
       </c>
       <c r="J81" t="s">
-        <v>246</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="E82" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" t="s">
-        <v>248</v>
+        <v>249</v>
+      </c>
+      <c r="I82" t="s">
+        <v>250</v>
       </c>
       <c r="J82" t="s">
-        <v>249</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="D83" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H83" t="s">
-        <v>251</v>
+        <v>252</v>
+      </c>
+      <c r="I83" t="s">
+        <v>253</v>
       </c>
       <c r="J83" t="s">
-        <v>252</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="E84" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H84" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="I84" t="s">
+        <v>256</v>
       </c>
       <c r="J84" t="s">
-        <v>255</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="E85" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H85" t="s">
-        <v>257</v>
+        <v>258</v>
+      </c>
+      <c r="I85" t="s">
+        <v>259</v>
       </c>
       <c r="J85" t="s">
-        <v>258</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="E86" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H86" t="s">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="I86" t="s">
+        <v>262</v>
       </c>
       <c r="J86" t="s">
-        <v>261</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="D87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H87" t="s">
-        <v>263</v>
+        <v>264</v>
+      </c>
+      <c r="I87" t="s">
+        <v>265</v>
       </c>
       <c r="J87" t="s">
-        <v>264</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="E88" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H88" t="s">
-        <v>266</v>
+        <v>267</v>
+      </c>
+      <c r="I88" t="s">
+        <v>268</v>
       </c>
       <c r="J88" t="s">
-        <v>267</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="E89" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H89" t="s">
-        <v>269</v>
+        <v>270</v>
+      </c>
+      <c r="I89" t="s">
+        <v>271</v>
       </c>
       <c r="J89" t="s">
-        <v>270</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="E90" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H90" t="s">
-        <v>272</v>
+        <v>273</v>
+      </c>
+      <c r="I90" t="s">
+        <v>274</v>
       </c>
       <c r="J90" t="s">
-        <v>273</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="E91" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H91" t="s">
-        <v>275</v>
+        <v>276</v>
+      </c>
+      <c r="I91" t="s">
+        <v>277</v>
       </c>
       <c r="J91" t="s">
-        <v>276</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="C92" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H92" t="s">
-        <v>278</v>
+        <v>279</v>
+      </c>
+      <c r="I92" t="s">
+        <v>280</v>
       </c>
       <c r="J92" t="s">
-        <v>279</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="D93" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H93" t="s">
-        <v>281</v>
+        <v>282</v>
+      </c>
+      <c r="I93" t="s">
+        <v>283</v>
       </c>
       <c r="J93" t="s">
-        <v>282</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="E94" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H94" t="s">
-        <v>284</v>
+        <v>285</v>
+      </c>
+      <c r="I94" t="s">
+        <v>286</v>
       </c>
       <c r="J94" t="s">
-        <v>285</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="F95" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H95" t="s">
-        <v>287</v>
+        <v>288</v>
+      </c>
+      <c r="I95" t="s">
+        <v>289</v>
       </c>
       <c r="J95" t="s">
-        <v>288</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="F96" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H96" t="s">
-        <v>290</v>
+        <v>291</v>
+      </c>
+      <c r="I96" t="s">
+        <v>292</v>
       </c>
       <c r="J96" t="s">
-        <v>291</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:10">
       <c r="E97" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H97" t="s">
-        <v>293</v>
+        <v>294</v>
+      </c>
+      <c r="I97" t="s">
+        <v>295</v>
       </c>
       <c r="J97" t="s">
-        <v>294</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="F98" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H98" t="s">
-        <v>296</v>
+        <v>297</v>
+      </c>
+      <c r="I98" t="s">
+        <v>298</v>
       </c>
       <c r="J98" t="s">
-        <v>297</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="E99" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H99" t="s">
-        <v>299</v>
+        <v>300</v>
+      </c>
+      <c r="I99" t="s">
+        <v>301</v>
       </c>
       <c r="J99" t="s">
-        <v>300</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:10">
       <c r="F100" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H100" t="s">
-        <v>302</v>
+        <v>303</v>
+      </c>
+      <c r="I100" t="s">
+        <v>304</v>
       </c>
       <c r="J100" t="s">
-        <v>303</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:10">
       <c r="D101" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H101" t="s">
-        <v>305</v>
+        <v>306</v>
+      </c>
+      <c r="I101" t="s">
+        <v>307</v>
       </c>
       <c r="J101" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:10">
       <c r="E102" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H102" t="s">
-        <v>308</v>
+        <v>309</v>
+      </c>
+      <c r="I102" t="s">
+        <v>310</v>
       </c>
       <c r="J102" t="s">
-        <v>309</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:10">
       <c r="F103" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H103" t="s">
-        <v>311</v>
+        <v>312</v>
+      </c>
+      <c r="I103" t="s">
+        <v>313</v>
       </c>
       <c r="J103" t="s">
-        <v>312</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:10">
       <c r="E104" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H104" t="s">
-        <v>314</v>
+        <v>315</v>
+      </c>
+      <c r="I104" t="s">
+        <v>316</v>
       </c>
       <c r="J104" t="s">
-        <v>315</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:10">
       <c r="F105" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H105" t="s">
-        <v>317</v>
+        <v>318</v>
+      </c>
+      <c r="I105" t="s">
+        <v>319</v>
       </c>
       <c r="J105" t="s">
-        <v>318</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:10">
       <c r="E106" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H106" t="s">
-        <v>320</v>
+        <v>321</v>
+      </c>
+      <c r="I106" t="s">
+        <v>322</v>
       </c>
       <c r="J106" t="s">
-        <v>321</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:10">
       <c r="F107" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H107" t="s">
-        <v>323</v>
+        <v>324</v>
+      </c>
+      <c r="I107" t="s">
+        <v>325</v>
       </c>
       <c r="J107" t="s">
-        <v>324</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:10">
       <c r="C108" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H108" t="s">
-        <v>326</v>
+        <v>327</v>
+      </c>
+      <c r="I108" t="s">
+        <v>328</v>
       </c>
       <c r="J108" t="s">
-        <v>327</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:10">
       <c r="D109" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H109" t="s">
-        <v>329</v>
+        <v>330</v>
+      </c>
+      <c r="I109" t="s">
+        <v>331</v>
       </c>
       <c r="J109" t="s">
-        <v>330</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:10">
       <c r="E110" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H110" t="s">
-        <v>332</v>
+        <v>333</v>
+      </c>
+      <c r="I110" t="s">
+        <v>334</v>
       </c>
       <c r="J110" t="s">
-        <v>333</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:10">
       <c r="E111" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H111" t="s">
-        <v>335</v>
+        <v>336</v>
+      </c>
+      <c r="I111" t="s">
+        <v>337</v>
       </c>
       <c r="J111" t="s">
-        <v>336</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:10">
       <c r="D112" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H112" t="s">
-        <v>338</v>
+        <v>339</v>
+      </c>
+      <c r="I112" t="s">
+        <v>340</v>
       </c>
       <c r="J112" t="s">
-        <v>339</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:10">
       <c r="E113" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H113" t="s">
-        <v>341</v>
+        <v>342</v>
+      </c>
+      <c r="I113" t="s">
+        <v>343</v>
       </c>
       <c r="J113" t="s">
-        <v>342</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:10">
       <c r="E114" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H114" t="s">
-        <v>344</v>
+        <v>345</v>
+      </c>
+      <c r="I114" t="s">
+        <v>346</v>
       </c>
       <c r="J114" t="s">
-        <v>345</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:10">
       <c r="D115" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H115" t="s">
-        <v>347</v>
+        <v>348</v>
+      </c>
+      <c r="I115" t="s">
+        <v>349</v>
       </c>
       <c r="J115" t="s">
-        <v>348</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:10">
       <c r="E116" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H116" t="s">
-        <v>350</v>
+        <v>351</v>
+      </c>
+      <c r="I116" t="s">
+        <v>352</v>
       </c>
       <c r="J116" t="s">
-        <v>351</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:10">
       <c r="E117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H117" t="s">
-        <v>353</v>
+        <v>354</v>
+      </c>
+      <c r="I117" t="s">
+        <v>355</v>
       </c>
       <c r="J117" t="s">
-        <v>354</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:10">
       <c r="E118" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H118" t="s">
-        <v>356</v>
+        <v>357</v>
+      </c>
+      <c r="I118" t="s">
+        <v>358</v>
       </c>
       <c r="J118" t="s">
-        <v>357</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:10">
       <c r="C119" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H119" t="s">
-        <v>359</v>
+        <v>360</v>
+      </c>
+      <c r="I119" t="s">
+        <v>361</v>
       </c>
       <c r="J119" t="s">
-        <v>360</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:10">
       <c r="D120" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H120" t="s">
-        <v>362</v>
+        <v>363</v>
+      </c>
+      <c r="I120" t="s">
+        <v>364</v>
       </c>
       <c r="J120" t="s">
-        <v>363</v>
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:10">
       <c r="D121" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H121" t="s">
-        <v>365</v>
+        <v>366</v>
+      </c>
+      <c r="I121" t="s">
+        <v>367</v>
       </c>
       <c r="J121" t="s">
-        <v>366</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:10">
       <c r="E122" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H122" t="s">
-        <v>368</v>
+        <v>369</v>
+      </c>
+      <c r="I122" t="s">
+        <v>370</v>
       </c>
       <c r="J122" t="s">
-        <v>369</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:10">
       <c r="E123" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H123" t="s">
-        <v>371</v>
+        <v>372</v>
+      </c>
+      <c r="I123" t="s">
+        <v>373</v>
       </c>
       <c r="J123" t="s">
-        <v>372</v>
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:10">
       <c r="D124" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H124" t="s">
-        <v>374</v>
+        <v>375</v>
+      </c>
+      <c r="I124" t="s">
+        <v>376</v>
       </c>
       <c r="J124" t="s">
-        <v>375</v>
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:10">
       <c r="E125" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H125" t="s">
-        <v>377</v>
+        <v>378</v>
+      </c>
+      <c r="I125" t="s">
+        <v>379</v>
       </c>
       <c r="J125" t="s">
-        <v>378</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:10">
       <c r="E126" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H126" t="s">
-        <v>380</v>
+        <v>381</v>
+      </c>
+      <c r="I126" t="s">
+        <v>382</v>
       </c>
       <c r="J126" t="s">
-        <v>381</v>
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:10">
       <c r="D127" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H127" t="s">
-        <v>383</v>
+        <v>384</v>
+      </c>
+      <c r="I127" t="s">
+        <v>385</v>
       </c>
       <c r="J127" t="s">
-        <v>384</v>
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:10">
       <c r="E128" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H128" t="s">
-        <v>386</v>
+        <v>387</v>
+      </c>
+      <c r="I128" t="s">
+        <v>388</v>
       </c>
       <c r="J128" t="s">
-        <v>387</v>
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:10">
       <c r="E129" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H129" t="s">
-        <v>389</v>
+        <v>390</v>
+      </c>
+      <c r="I129" t="s">
+        <v>391</v>
       </c>
       <c r="J129" t="s">
-        <v>390</v>
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:10">
       <c r="E130" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H130" t="s">
-        <v>392</v>
+        <v>393</v>
+      </c>
+      <c r="I130" t="s">
+        <v>394</v>
       </c>
       <c r="J130" t="s">
-        <v>393</v>
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:10">
       <c r="C131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H131" t="s">
-        <v>395</v>
+        <v>396</v>
+      </c>
+      <c r="I131" t="s">
+        <v>397</v>
       </c>
       <c r="J131" t="s">
-        <v>396</v>
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:10">
       <c r="D132" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H132" t="s">
-        <v>398</v>
+        <v>399</v>
+      </c>
+      <c r="I132" t="s">
+        <v>400</v>
       </c>
       <c r="J132" t="s">
-        <v>399</v>
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:10">
       <c r="E133" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H133" t="s">
-        <v>401</v>
+        <v>402</v>
+      </c>
+      <c r="I133" t="s">
+        <v>403</v>
       </c>
       <c r="J133" t="s">
-        <v>402</v>
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:10">
       <c r="E134" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H134" t="s">
-        <v>404</v>
+        <v>405</v>
+      </c>
+      <c r="I134" t="s">
+        <v>406</v>
       </c>
       <c r="J134" t="s">
-        <v>405</v>
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:10">
       <c r="E135" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H135" t="s">
-        <v>407</v>
+        <v>408</v>
+      </c>
+      <c r="I135" t="s">
+        <v>409</v>
       </c>
       <c r="J135" t="s">
-        <v>408</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:10">
       <c r="D136" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H136" t="s">
-        <v>410</v>
+        <v>411</v>
+      </c>
+      <c r="I136" t="s">
+        <v>412</v>
       </c>
       <c r="J136" t="s">
-        <v>411</v>
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:10">
       <c r="E137" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H137" t="s">
-        <v>413</v>
+        <v>414</v>
+      </c>
+      <c r="I137" t="s">
+        <v>415</v>
       </c>
       <c r="J137" t="s">
-        <v>414</v>
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:10">
       <c r="E138" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H138" t="s">
-        <v>416</v>
+        <v>417</v>
+      </c>
+      <c r="I138" t="s">
+        <v>418</v>
       </c>
       <c r="J138" t="s">
-        <v>417</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:10">
       <c r="D139" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H139" t="s">
-        <v>419</v>
+        <v>420</v>
+      </c>
+      <c r="I139" t="s">
+        <v>421</v>
       </c>
       <c r="J139" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:10">
       <c r="E140" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H140" t="s">
-        <v>422</v>
+        <v>423</v>
+      </c>
+      <c r="I140" t="s">
+        <v>424</v>
       </c>
       <c r="J140" t="s">
-        <v>423</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:10">
       <c r="E141" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H141" t="s">
-        <v>425</v>
+        <v>426</v>
+      </c>
+      <c r="I141" t="s">
+        <v>427</v>
       </c>
       <c r="J141" t="s">
-        <v>426</v>
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:10">
       <c r="C142" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H142" t="s">
-        <v>428</v>
+        <v>429</v>
+      </c>
+      <c r="I142" t="s">
+        <v>430</v>
       </c>
       <c r="J142" t="s">
-        <v>429</v>
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:10">
       <c r="D143" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H143" t="s">
-        <v>431</v>
+        <v>432</v>
+      </c>
+      <c r="I143" t="s">
+        <v>433</v>
       </c>
       <c r="J143" t="s">
-        <v>432</v>
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:10">
       <c r="E144" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H144" t="s">
-        <v>434</v>
+        <v>435</v>
+      </c>
+      <c r="I144" t="s">
+        <v>436</v>
       </c>
       <c r="J144" t="s">
-        <v>435</v>
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:10">
       <c r="E145" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H145" t="s">
-        <v>437</v>
+        <v>438</v>
+      </c>
+      <c r="I145" t="s">
+        <v>439</v>
       </c>
       <c r="J145" t="s">
-        <v>438</v>
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:10">
       <c r="E146" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H146" t="s">
-        <v>440</v>
+        <v>441</v>
+      </c>
+      <c r="I146" t="s">
+        <v>442</v>
       </c>
       <c r="J146" t="s">
-        <v>441</v>
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:10">
       <c r="D147" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G147" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H147" t="s">
-        <v>444</v>
+        <v>445</v>
+      </c>
+      <c r="I147" t="s">
+        <v>446</v>
       </c>
       <c r="J147" t="s">
-        <v>445</v>
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:10">
       <c r="E148" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H148" t="s">
-        <v>447</v>
+        <v>448</v>
+      </c>
+      <c r="I148" t="s">
+        <v>449</v>
       </c>
       <c r="J148" t="s">
-        <v>448</v>
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:10">
       <c r="E149" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H149" t="s">
-        <v>450</v>
+        <v>451</v>
+      </c>
+      <c r="I149" t="s">
+        <v>452</v>
       </c>
       <c r="J149" t="s">
-        <v>451</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:10">
       <c r="E150" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G150" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H150" t="s">
-        <v>454</v>
+        <v>455</v>
+      </c>
+      <c r="I150" t="s">
+        <v>456</v>
       </c>
       <c r="J150" t="s">
-        <v>455</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:10">
       <c r="D151" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H151" t="s">
-        <v>457</v>
+        <v>458</v>
+      </c>
+      <c r="I151" t="s">
+        <v>459</v>
       </c>
       <c r="J151" t="s">
-        <v>458</v>
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:10">
       <c r="E152" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H152" t="s">
-        <v>460</v>
+        <v>461</v>
+      </c>
+      <c r="I152" t="s">
+        <v>462</v>
       </c>
       <c r="J152" t="s">
-        <v>461</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:10">
       <c r="E153" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H153" t="s">
-        <v>463</v>
+        <v>464</v>
+      </c>
+      <c r="I153" t="s">
+        <v>465</v>
       </c>
       <c r="J153" t="s">
-        <v>464</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:10">
       <c r="D154" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H154" t="s">
-        <v>466</v>
+        <v>467</v>
+      </c>
+      <c r="I154" t="s">
+        <v>468</v>
       </c>
       <c r="J154" t="s">
-        <v>467</v>
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:10">
       <c r="E155" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H155" t="s">
-        <v>469</v>
+        <v>470</v>
+      </c>
+      <c r="I155" t="s">
+        <v>471</v>
       </c>
       <c r="J155" t="s">
-        <v>470</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:10">
       <c r="E156" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H156" t="s">
-        <v>472</v>
+        <v>473</v>
+      </c>
+      <c r="I156" t="s">
+        <v>474</v>
       </c>
       <c r="J156" t="s">
-        <v>473</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:10">
       <c r="A157" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H157" t="s">
-        <v>475</v>
+        <v>476</v>
+      </c>
+      <c r="I157" t="s">
+        <v>477</v>
       </c>
       <c r="J157" t="s">
-        <v>476</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:10">
       <c r="B158" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H158" t="s">
-        <v>478</v>
+        <v>479</v>
+      </c>
+      <c r="I158" t="s">
+        <v>480</v>
       </c>
       <c r="J158" t="s">
-        <v>479</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:10">
       <c r="C159" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H159" t="s">
-        <v>481</v>
+        <v>482</v>
+      </c>
+      <c r="I159" t="s">
+        <v>483</v>
       </c>
       <c r="J159" t="s">
-        <v>482</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:10">
       <c r="D160" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H160" t="s">
-        <v>484</v>
+        <v>485</v>
+      </c>
+      <c r="I160" t="s">
+        <v>486</v>
       </c>
       <c r="J160" t="s">
-        <v>485</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:10">
       <c r="D161" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H161" t="s">
-        <v>487</v>
+        <v>488</v>
+      </c>
+      <c r="I161" t="s">
+        <v>489</v>
       </c>
       <c r="J161" t="s">
-        <v>488</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:10">
       <c r="D162" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H162" t="s">
-        <v>490</v>
+        <v>491</v>
+      </c>
+      <c r="I162" t="s">
+        <v>492</v>
       </c>
       <c r="J162" t="s">
-        <v>491</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:10">
       <c r="C163" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H163" t="s">
-        <v>493</v>
+        <v>494</v>
+      </c>
+      <c r="I163" t="s">
+        <v>495</v>
       </c>
       <c r="J163" t="s">
-        <v>494</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:10">
       <c r="D164" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H164" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="I164" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="J164" t="s">
-        <v>497</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:10">
       <c r="D165" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H165" t="s">
-        <v>499</v>
+        <v>500</v>
+      </c>
+      <c r="I165" t="s">
+        <v>501</v>
       </c>
       <c r="J165" t="s">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:10">
       <c r="D166" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H166" t="s">
-        <v>502</v>
+        <v>503</v>
+      </c>
+      <c r="I166" t="s">
+        <v>504</v>
       </c>
       <c r="J166" t="s">
-        <v>503</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:10">
       <c r="C167" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H167" t="s">
-        <v>505</v>
+        <v>506</v>
+      </c>
+      <c r="I167" t="s">
+        <v>507</v>
       </c>
       <c r="J167" t="s">
-        <v>506</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:10">
       <c r="D168" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H168" t="s">
-        <v>508</v>
+        <v>509</v>
+      </c>
+      <c r="I168" t="s">
+        <v>510</v>
       </c>
       <c r="J168" t="s">
-        <v>509</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:10">
       <c r="D169" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H169" t="s">
-        <v>511</v>
+        <v>512</v>
+      </c>
+      <c r="I169" t="s">
+        <v>513</v>
       </c>
       <c r="J169" t="s">
-        <v>512</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:10">
       <c r="D170" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H170" t="s">
-        <v>514</v>
+        <v>515</v>
+      </c>
+      <c r="I170" t="s">
+        <v>516</v>
       </c>
       <c r="J170" t="s">
-        <v>515</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:10">
       <c r="D171" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H171" t="s">
-        <v>517</v>
+        <v>518</v>
+      </c>
+      <c r="I171" t="s">
+        <v>519</v>
       </c>
       <c r="J171" t="s">
-        <v>518</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:10">
       <c r="B172" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H172" t="s">
-        <v>520</v>
+        <v>521</v>
+      </c>
+      <c r="I172" t="s">
+        <v>522</v>
       </c>
       <c r="J172" t="s">
-        <v>521</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:10">
       <c r="C173" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H173" t="s">
-        <v>523</v>
+        <v>524</v>
+      </c>
+      <c r="I173" t="s">
+        <v>525</v>
       </c>
       <c r="J173" t="s">
-        <v>524</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:10">
       <c r="C174" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H174" t="s">
-        <v>526</v>
+        <v>527</v>
+      </c>
+      <c r="I174" t="s">
+        <v>528</v>
       </c>
       <c r="J174" t="s">
-        <v>527</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:10">
       <c r="C175" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H175" t="s">
-        <v>529</v>
+        <v>530</v>
+      </c>
+      <c r="I175" t="s">
+        <v>531</v>
       </c>
       <c r="J175" t="s">
-        <v>530</v>
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:10">
       <c r="C176" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H176" t="s">
-        <v>532</v>
+        <v>533</v>
+      </c>
+      <c r="I176" t="s">
+        <v>534</v>
       </c>
       <c r="J176" t="s">
-        <v>533</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:10">
       <c r="B177" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H177" t="s">
-        <v>535</v>
+        <v>536</v>
+      </c>
+      <c r="I177" t="s">
+        <v>537</v>
       </c>
       <c r="J177" t="s">
-        <v>536</v>
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:10">
       <c r="A178" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H178" t="s">
-        <v>538</v>
+        <v>539</v>
+      </c>
+      <c r="I178" t="s">
+        <v>540</v>
       </c>
       <c r="J178" t="s">
-        <v>539</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
